--- a/.claude/skills/AutoCaseReview/inputs/requirement_data/（新）iBatchInsight-迭代-CPV-SP7-需求.xlsx
+++ b/.claude/skills/AutoCaseReview/inputs/requirement_data/（新）iBatchInsight-迭代-CPV-SP7-需求.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11008"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hml/Documents/Study/AI/AutoCaseReview/.claude/skills/AutoCaseReview/inputs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0057E705-5BB5-DF4A-BCB3-7F7D7977CD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27660" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="（新）iBatchInsight-迭代-CPV-SP7-需求" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -32,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -58,6 +53,18 @@
     <t>创建者</t>
   </si>
   <si>
+    <t>所属迭代</t>
+  </si>
+  <si>
+    <t>待办事项1</t>
+  </si>
+  <si>
+    <t>待办事项2</t>
+  </si>
+  <si>
+    <t>待办事项3</t>
+  </si>
+  <si>
     <t>#203726</t>
   </si>
   <si>
@@ -79,13 +86,22 @@
     <t>荆慧慧</t>
   </si>
   <si>
+    <t>CPV-SP7</t>
+  </si>
+  <si>
+    <t>等级为2个时，删除按钮禁用 @黄美玲 修改用例,不以prd为准</t>
+  </si>
+  <si>
+    <t>最小值和最大值都为空的时候提示和qrs保持统一，均为：最小值和最大值至少输入一项 @黄美玲 修改用例,不以prd为准</t>
+  </si>
+  <si>
     <t>#202008</t>
   </si>
   <si>
     <t>【插件化】-分析配置与执行-NP控制图</t>
   </si>
   <si>
-    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22344/12001/3</t>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22315/undefined/0</t>
   </si>
   <si>
     <t>吴璟</t>
@@ -94,13 +110,19 @@
     <t>糜德明</t>
   </si>
   <si>
+    <t>纵轴变量下存在小数、负数或时分秒格式数据，阻止分析，提示：纵轴变量未包含大于等于0的整数，暂不支持分析 @荆慧慧 补充prd  @黄美玲 修改用例</t>
+  </si>
+  <si>
     <t>#202007</t>
   </si>
   <si>
     <t>【插件化】-分析配置与执行-P控制图</t>
   </si>
   <si>
-    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22300/undefined/0?uid=g8x2nrfb8xvn</t>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22300/undefined/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大值、最小值、平均值、UCL、LCL受小数保留位数影响 @荆慧慧 补充prd  </t>
   </si>
   <si>
     <t>#204293</t>
@@ -109,21 +131,33 @@
     <t>【审计追踪】- 1业务站点-角色管理审计内容优化</t>
   </si>
   <si>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22293/undefined/0</t>
+  </si>
+  <si>
     <t>唐尧</t>
   </si>
   <si>
+    <t>删除/批量删除审计详情，不显示分配用户信息@唐尧 修改prd @黄美玲 修改用例</t>
+  </si>
+  <si>
     <t>#203719</t>
   </si>
   <si>
     <t>【UI】优化数据分析工作台交互</t>
   </si>
   <si>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22299/undefined/0</t>
+  </si>
+  <si>
     <t>#186797</t>
   </si>
   <si>
     <t>【插件化】-分析配置与执行-配对T检验</t>
   </si>
   <si>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22248/undefined/0</t>
+  </si>
+  <si>
     <t>牛文俐</t>
   </si>
   <si>
@@ -136,63 +170,55 @@
     <t>【工艺能力汇总】支持导出PDF文件</t>
   </si>
   <si>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22297/undefined/0</t>
+  </si>
+  <si>
+    <t>若某监控项目无异常批次，显示“0” @荆慧慧 修改prd @黄美玲 修改用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">表格列增加异常规则列 @荆慧慧 补充prd </t>
+  </si>
+  <si>
     <t>#195198</t>
   </si>
   <si>
     <t>【导入导出】-角色管理</t>
   </si>
   <si>
-    <t>代办事项1@责任人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>代办事项2@责任人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>代办事项3@责任人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>预览和编辑使用同一个组件，预览弹框内是不可编辑 @黄美玲 修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级为2个时，删除按钮禁用 @黄美玲  修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>最小值等于最大值的时候和qrs的提示语保持一致，均为：最小值需要小于最大值@黄美玲  修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>平均值、UCL、LCL受小数保留位数影响 @荆慧慧 补充prd  @黄美玲 修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>纵轴变量下存在小数、负数或时分秒格式数据，阻止分析，提示：纵轴变量未包含大于等于0的整数，暂不支持分析  @荆慧慧 补充prd  @黄美玲 修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大值、最小值、平均值、UCL、LCL受小数保留位数影响  @荆慧慧 补充prd  @黄美玲 修改用例</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属迭代</t>
-  </si>
-  <si>
-    <t>CPV-SP7</t>
+    <t>http://testbench.leateckgroup.com:8081/#/track/case/caseDetail/1/22295/undefined/0</t>
+  </si>
+  <si>
+    <t>文件大小不限制20MB，文件限制2000条数据@唐尧 修改prd @黄美玲 修改用例</t>
+  </si>
+  <si>
+    <t>不勾选角色，则导出全量数据@唐尧 修改prd @黄美玲 修改用例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基于当前筛选条件进行导出，该功能不做 @唐尧 修改prd </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -200,36 +226,334 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线 Light"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -237,261 +561,333 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -507,7 +903,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -519,7 +915,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -538,7 +934,7 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -573,7 +969,7 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -742,20 +1138,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <cols>
-    <col min="2" max="2" width="43.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="46.9333333333333" customWidth="1"/>
+    <col min="11" max="11" width="18.8833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -784,265 +1177,279 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>46197</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1">
         <v>46198</v>
       </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
+      <c r="J3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1">
         <v>46198</v>
       </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>43</v>
+      <c r="J4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
       </c>
       <c r="E5" s="1">
         <v>46205</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="2"/>
+      <c r="J5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
       </c>
       <c r="E6" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
       </c>
       <c r="E7" s="1">
         <v>46200</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="2"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
       </c>
       <c r="E8" s="1">
         <v>46204</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
       </c>
       <c r="E9" s="1">
         <v>46204</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="J1" r:id="rId1" xr:uid="{AD77AE0F-A581-CD4C-922E-195BE360A9D8}"/>
-    <hyperlink ref="K1" r:id="rId2" xr:uid="{5D7B2E29-1F7B-6B4B-B50A-CEC6D7F77ED0}"/>
-    <hyperlink ref="L1" r:id="rId3" xr:uid="{5FDC7450-B1C0-BE4E-AC3D-B35416FC3E0A}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>